--- a/guests.xlsx
+++ b/guests.xlsx
@@ -484,7 +484,7 @@
         <v>Hoffmann</v>
       </c>
       <c r="C8" t="str">
-        <v>Tisch 2 - Lavendel</v>
+        <v>moin</v>
       </c>
     </row>
     <row r="9">
@@ -506,7 +506,7 @@
         <v>Wagner</v>
       </c>
       <c r="C10" t="str">
-        <v>Tisch 3 - Pfingstrose</v>
+        <v>moin</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         <v>Schulz</v>
       </c>
       <c r="C14" t="str">
-        <v>Tisch 5 - Kamille</v>
+        <v>Tisch 2 - Lavendel</v>
       </c>
     </row>
     <row r="15">
@@ -561,7 +561,7 @@
         <v>Schulz</v>
       </c>
       <c r="C15" t="str">
-        <v>Tisch 5 - Kamille</v>
+        <v>moin</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         <v>Zimmermann</v>
       </c>
       <c r="C18" t="str">
-        <v>Tisch 6 - Vergissmeinnicht</v>
+        <v>moin</v>
       </c>
     </row>
     <row r="19">

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -473,7 +473,7 @@
         <v>Weber</v>
       </c>
       <c r="C7" t="str">
-        <v>Tisch 2 - Lavendel</v>
+        <v>Tisch 7 - Sonnenblume</v>
       </c>
     </row>
     <row r="8">
@@ -641,9 +641,31 @@
         <v>Tisch 5 - Kamille</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Marvin</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Loedgin</v>
+      </c>
+      <c r="C23" t="str">
+        <v>moin</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">Henriette </v>
+      </c>
+      <c r="B24" t="str">
+        <v>Niermann</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Tisch 4 - Flieder</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -654,7 +654,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">Henriette </v>
+        <v>Henriette</v>
       </c>
       <c r="B24" t="str">
         <v>Niermann</v>

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -484,7 +484,7 @@
         <v>Hoffmann</v>
       </c>
       <c r="C8" t="str">
-        <v>moin</v>
+        <v>Tisch 5 - Kamille</v>
       </c>
     </row>
     <row r="9">
@@ -506,7 +506,7 @@
         <v>Wagner</v>
       </c>
       <c r="C10" t="str">
-        <v>moin</v>
+        <v>Tisch 5 - Kamille</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
         <v>Schulz</v>
       </c>
       <c r="C15" t="str">
-        <v>moin</v>
+        <v>Tisch 3 - Pfingstrose</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         <v>Zimmermann</v>
       </c>
       <c r="C18" t="str">
-        <v>moin</v>
+        <v>Tisch 6 - Vergissmeinnicht</v>
       </c>
     </row>
     <row r="19">
@@ -649,7 +649,7 @@
         <v>Loedgin</v>
       </c>
       <c r="C23" t="str">
-        <v>moin</v>
+        <v>Tisch 6 - Vergissmeinnicht</v>
       </c>
     </row>
     <row r="24">

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -693,9 +693,23 @@
         <v>tr</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">Paul </v>
+      </c>
+      <c r="B22" t="str">
+        <v>Meyer</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>de</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -449,7 +449,7 @@
         <v>Schmidt</v>
       </c>
       <c r="C4" t="str">
-        <v>Tisch 1 - Rose</v>
+        <v>Tisch 7 - Sonnenblume</v>
       </c>
       <c r="D4" t="str">
         <v>de</v>
@@ -687,7 +687,7 @@
         <v>Mustermann</v>
       </c>
       <c r="C21" t="str">
-        <v>Tisch 7 - Sonnenblume</v>
+        <v>Tisch 1 - Rose</v>
       </c>
       <c r="D21" t="str">
         <v>tr</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">Paul </v>
+        <v>Paul</v>
       </c>
       <c r="B22" t="str">
         <v>Meyer</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>Tisch 6 - Vergissmeinnicht</v>
       </c>
       <c r="D22" t="str">
         <v>de</v>

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -707,9 +707,23 @@
         <v>de</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">Devin </v>
+      </c>
+      <c r="B23" t="str">
+        <v>Borchers</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Tisch 2 - Lavendel</v>
+      </c>
+      <c r="D23" t="str">
+        <v>de</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -709,7 +709,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">Devin </v>
+        <v>Devin</v>
       </c>
       <c r="B23" t="str">
         <v>Borchers</v>
@@ -721,9 +721,37 @@
         <v>de</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Marvin</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Loeding</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Tisch 4 - Flieder</v>
+      </c>
+      <c r="D24" t="str">
+        <v>de</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve">Henriette </v>
+      </c>
+      <c r="B25" t="str">
+        <v>Niermann</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>de</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -737,13 +737,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">Henriette </v>
+        <v>Henriette</v>
       </c>
       <c r="B25" t="str">
         <v>Niermann</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>Tisch 2 - Lavendel</v>
       </c>
       <c r="D25" t="str">
         <v>de</v>

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -630,9 +630,31 @@
         <v>Tisch 7 - Sonnenblume</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">Marvin </v>
+      </c>
+      <c r="B22" t="str">
+        <v>Loeding</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Tisch 5 - Kamille</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">Henriette </v>
+      </c>
+      <c r="B23" t="str">
+        <v>Niermann</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Tisch 1 - Rose</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -632,7 +632,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">Marvin </v>
+        <v>Marvin</v>
       </c>
       <c r="B22" t="str">
         <v>Loeding</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">Henriette </v>
+        <v>Henriette</v>
       </c>
       <c r="B23" t="str">
         <v>Niermann</v>

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C177"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,249 +412,1943 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Anna</v>
+        <v>Luisa</v>
       </c>
       <c r="B2" t="str">
-        <v>Meier</v>
+        <v>Demirci</v>
       </c>
       <c r="C2" t="str">
-        <v>Tisch 1 - Rose</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Anna</v>
+        <v>Ibrahim</v>
       </c>
       <c r="B3" t="str">
-        <v>Mayer</v>
+        <v>Demirci</v>
       </c>
       <c r="C3" t="str">
-        <v>Tisch 4 - Flieder</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Thomas</v>
+        <v>Luca Emma</v>
       </c>
       <c r="B4" t="str">
-        <v>Schmidt</v>
+        <v>Schner</v>
       </c>
       <c r="C4" t="str">
-        <v>Tisch 1 - Rose</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Julia</v>
+        <v>Viktor</v>
       </c>
       <c r="B5" t="str">
-        <v>Schmidt</v>
+        <v>Schner</v>
       </c>
       <c r="C5" t="str">
-        <v>Tisch 1 - Rose</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Michael</v>
+        <v>Canan</v>
       </c>
       <c r="B6" t="str">
-        <v>Weber</v>
+        <v>Brandt</v>
       </c>
       <c r="C6" t="str">
-        <v>Tisch 2 - Lavendel</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sarah</v>
+        <v>Hakan</v>
       </c>
       <c r="B7" t="str">
-        <v>Weber</v>
+        <v>Toplar</v>
       </c>
       <c r="C7" t="str">
-        <v>Tisch 2 - Lavendel</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lukas</v>
+        <v>Dilara</v>
       </c>
       <c r="B8" t="str">
-        <v>Hoffmann</v>
+        <v>Toplar</v>
       </c>
       <c r="C8" t="str">
-        <v>Tisch 2 - Lavendel</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Sophie</v>
+        <v>Samet</v>
       </c>
       <c r="B9" t="str">
-        <v>Wagner</v>
+        <v>Demirci</v>
       </c>
       <c r="C9" t="str">
-        <v>Tisch 3 - Pfingstrose</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Jonas</v>
+        <v>Mama</v>
       </c>
       <c r="B10" t="str">
-        <v>Wagner</v>
+        <v>Bente</v>
       </c>
       <c r="C10" t="str">
-        <v>Tisch 3 - Pfingstrose</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Emma</v>
+        <v>Papa</v>
       </c>
       <c r="B11" t="str">
-        <v>Fischer</v>
+        <v>Bente</v>
       </c>
       <c r="C11" t="str">
-        <v>Tisch 3 - Pfingstrose</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Paul</v>
+        <v>Leonie</v>
       </c>
       <c r="B12" t="str">
-        <v>Becker</v>
+        <v>Bente</v>
       </c>
       <c r="C12" t="str">
-        <v>Tisch 4 - Flieder</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Laura</v>
+        <v>Christoph</v>
       </c>
       <c r="B13" t="str">
-        <v>Becker</v>
+        <v>Gurok</v>
       </c>
       <c r="C13" t="str">
-        <v>Tisch 4 - Flieder</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Felix</v>
+        <v>Birgit</v>
       </c>
       <c r="B14" t="str">
-        <v>Schulz</v>
+        <v>Möller</v>
       </c>
       <c r="C14" t="str">
-        <v>Tisch 5 - Kamille</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Marie</v>
+        <v>Christian</v>
       </c>
       <c r="B15" t="str">
-        <v>Schulz</v>
+        <v>Möller</v>
       </c>
       <c r="C15" t="str">
-        <v>Tisch 5 - Kamille</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>David</v>
+        <v>Teresa</v>
       </c>
       <c r="B16" t="str">
-        <v>Klein</v>
+        <v>Möller</v>
       </c>
       <c r="C16" t="str">
-        <v>Tisch 5 - Kamille</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Hannah</v>
+        <v>Tina</v>
       </c>
       <c r="B17" t="str">
-        <v>Braun</v>
+        <v>Hansen</v>
       </c>
       <c r="C17" t="str">
-        <v>Tisch 6 - Vergissmeinnicht</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Simon</v>
+        <v>Lisann</v>
       </c>
       <c r="B18" t="str">
-        <v>Zimmermann</v>
+        <v>Eckert</v>
       </c>
       <c r="C18" t="str">
-        <v>Tisch 6 - Vergissmeinnicht</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lena</v>
+        <v>Fynn</v>
       </c>
       <c r="B19" t="str">
-        <v>Krueger</v>
+        <v>Eckert</v>
       </c>
       <c r="C19" t="str">
-        <v>Tisch 6 - Vergissmeinnicht</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Max</v>
+        <v>Lisa</v>
       </c>
       <c r="B20" t="str">
-        <v>Mustermann</v>
+        <v>Schröder</v>
       </c>
       <c r="C20" t="str">
-        <v>Tisch 7 - Sonnenblume</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Nina</v>
+        <v>Olaf</v>
       </c>
       <c r="B21" t="str">
-        <v>Mustermann</v>
+        <v>Hansen</v>
       </c>
       <c r="C21" t="str">
-        <v>Tisch 7 - Sonnenblume</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Marvin</v>
+        <v>Olaf</v>
       </c>
       <c r="B22" t="str">
-        <v>Loeding</v>
+        <v>Freundin</v>
       </c>
       <c r="C22" t="str">
-        <v>Tisch 5 - Kamille</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>Tim</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Salenz</v>
+      </c>
+      <c r="C23" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Salenz</v>
+      </c>
+      <c r="C24" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Matthias</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Bente</v>
+      </c>
+      <c r="C25" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Bettina</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Bente</v>
+      </c>
+      <c r="C26" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Katharina</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Bente</v>
+      </c>
+      <c r="C27" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Antonia</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Bente</v>
+      </c>
+      <c r="C28" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Gaby</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Bente</v>
+      </c>
+      <c r="C29" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Rüdiger</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Bente</v>
+      </c>
+      <c r="C30" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Annem</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Babam</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Serpil</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Süleymann</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Berksan</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Emin</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Aslihan</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Mehmet</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C38" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Zeynep</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C39" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Emerican</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C40" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Sahin</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C41" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Sidica</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C42" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Yasin</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Demrici</v>
+      </c>
+      <c r="C43" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Yasim</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Demrici</v>
+      </c>
+      <c r="C44" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Eda</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Demirci</v>
+      </c>
+      <c r="C45" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Jenny</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Brandt</v>
+      </c>
+      <c r="C46" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Behram</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Brandt</v>
+      </c>
+      <c r="C47" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Naima</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Brandt</v>
+      </c>
+      <c r="C48" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Nico</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Bethien</v>
+      </c>
+      <c r="C49" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Yasin</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Brandt</v>
+      </c>
+      <c r="C50" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Lara</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Nicole</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Adrian</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Laura</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Peters</v>
+      </c>
+      <c r="C54" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Michael</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Weber</v>
+      </c>
+      <c r="C55" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Saskia</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Knop</v>
+      </c>
+      <c r="C56" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Fabian</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Bethien</v>
+      </c>
+      <c r="C57" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Lili</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Ulrich</v>
+      </c>
+      <c r="C58" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <v>Henriette</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B59" t="str">
         <v>Niermann</v>
       </c>
-      <c r="C23" t="str">
-        <v>Tisch 1 - Rose</v>
+      <c r="C59" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Antonia</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Schultz</v>
+      </c>
+      <c r="C60" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Kevin</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Klemm</v>
+      </c>
+      <c r="C61" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Caroline</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Schnelle</v>
+      </c>
+      <c r="C62" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Moritz</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Großmann</v>
+      </c>
+      <c r="C63" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Marvin</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Loeding</v>
+      </c>
+      <c r="C64" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Christina</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Stamp</v>
+      </c>
+      <c r="C65" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Anton</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Offner</v>
+      </c>
+      <c r="C66" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Mila</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Gastmann</v>
+      </c>
+      <c r="C67" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Merle</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Lehmann</v>
+      </c>
+      <c r="C68" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Aileen</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v/>
+      </c>
+      <c r="B70" t="str">
+        <v>Toplar</v>
+      </c>
+      <c r="C70" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v/>
+      </c>
+      <c r="B71" t="str">
+        <v>Toplar</v>
+      </c>
+      <c r="C71" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Bahar</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Toplar</v>
+      </c>
+      <c r="C72" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Merve</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Toplar</v>
+      </c>
+      <c r="C73" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Muhammed</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Toplar</v>
+      </c>
+      <c r="C74" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Hanifi</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Toplar</v>
+      </c>
+      <c r="C75" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Nadine</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Toplar</v>
+      </c>
+      <c r="C76" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Ali</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Sancak</v>
+      </c>
+      <c r="C77" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Navjot</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Sancak</v>
+      </c>
+      <c r="C78" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Semih</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Çakmakcı</v>
+      </c>
+      <c r="C79" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Asli</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Çakmakcı</v>
+      </c>
+      <c r="C80" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Yunus</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Motorrad</v>
+      </c>
+      <c r="C81" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Fatih</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Motorrad</v>
+      </c>
+      <c r="C82" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Aliye</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Avci</v>
+      </c>
+      <c r="C83" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Nazli</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Avci</v>
+      </c>
+      <c r="C84" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Mehmet</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Avci</v>
+      </c>
+      <c r="C85" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Ayten</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Müller</v>
+      </c>
+      <c r="C86" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Mira</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Müller</v>
+      </c>
+      <c r="C87" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Leyla</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Müller</v>
+      </c>
+      <c r="C88" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Deniz</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Üyen</v>
+      </c>
+      <c r="C89" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Nazli</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Üyen</v>
+      </c>
+      <c r="C90" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Melek</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Yilmaz</v>
+      </c>
+      <c r="C91" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Ali</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Yilmaz</v>
+      </c>
+      <c r="C92" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Hilal</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Bektas</v>
+      </c>
+      <c r="C93" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Eren</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Bektas</v>
+      </c>
+      <c r="C94" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Sultan</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Aksoy</v>
+      </c>
+      <c r="C95" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Seyma</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Aksoy</v>
+      </c>
+      <c r="C96" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Cevriye</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Seyhan</v>
+      </c>
+      <c r="C97" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Durgadin</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Bolat</v>
+      </c>
+      <c r="C98" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Mahmut</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Yildiz</v>
+      </c>
+      <c r="C99" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Mehmet</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Yildiz</v>
+      </c>
+      <c r="C100" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Serdal</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Sahin</v>
+      </c>
+      <c r="C101" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Saziye</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Sahin</v>
+      </c>
+      <c r="C102" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Sinan</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Emsal</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Vildan</v>
+      </c>
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Hamit</v>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Miriyam</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Rahimi</v>
+      </c>
+      <c r="C107" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Ali</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Rahimi</v>
+      </c>
+      <c r="C108" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Kacper</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Nowak</v>
+      </c>
+      <c r="C109" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Leonie</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Paulsen</v>
+      </c>
+      <c r="C110" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Özlem</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Yuvali</v>
+      </c>
+      <c r="C111" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Kubilay-Alpay</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Yuvali</v>
+      </c>
+      <c r="C112" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Ibrahim</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Özcan</v>
+      </c>
+      <c r="C113" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Rezal</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Yosofi</v>
+      </c>
+      <c r="C114" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Hanno</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Rencken</v>
+      </c>
+      <c r="C115" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Svende</v>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Robert</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Ladewig</v>
+      </c>
+      <c r="C117" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Lukas</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Tiede</v>
+      </c>
+      <c r="C118" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Paddy</v>
+      </c>
+      <c r="B119" t="str">
+        <v/>
+      </c>
+      <c r="C119" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Daniel</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Litzenberger</v>
+      </c>
+      <c r="C120" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Michi</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Nissen</v>
+      </c>
+      <c r="C121" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Nici</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Nissen</v>
+      </c>
+      <c r="C122" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Sebastian</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Hansen</v>
+      </c>
+      <c r="C123" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Imke</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Hansen</v>
+      </c>
+      <c r="C124" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Ridvan</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Canbul</v>
+      </c>
+      <c r="C125" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Nurgül</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Canbul</v>
+      </c>
+      <c r="C126" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Fatih</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Balkas</v>
+      </c>
+      <c r="C127" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Mirko</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Niemann</v>
+      </c>
+      <c r="C128" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Anissa</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Niemann</v>
+      </c>
+      <c r="C129" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Arne</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Steinfatt</v>
+      </c>
+      <c r="C130" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Sarah</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Steinfatt</v>
+      </c>
+      <c r="C131" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Marcel</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Petersen</v>
+      </c>
+      <c r="C132" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Stefanie</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Petersen</v>
+      </c>
+      <c r="C133" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Serhat</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Bakan</v>
+      </c>
+      <c r="C134" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Yasemin</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Bakan</v>
+      </c>
+      <c r="C135" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Aras</v>
+      </c>
+      <c r="B136" t="str">
+        <v/>
+      </c>
+      <c r="C136" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Kausar</v>
+      </c>
+      <c r="B137" t="str">
+        <v/>
+      </c>
+      <c r="C137" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Lawand</v>
+      </c>
+      <c r="B138" t="str">
+        <v/>
+      </c>
+      <c r="C138" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Fetanet</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Aksoy</v>
+      </c>
+      <c r="C139" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Adem</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Erim</v>
+      </c>
+      <c r="C140" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Isa</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Erim</v>
+      </c>
+      <c r="C141" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Wasim</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Haj Ali</v>
+      </c>
+      <c r="C142" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Jessica</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Haj Ali</v>
+      </c>
+      <c r="C143" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Emrah</v>
+      </c>
+      <c r="B144" t="str">
+        <v/>
+      </c>
+      <c r="C144" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Baran</v>
+      </c>
+      <c r="B145" t="str">
+        <v/>
+      </c>
+      <c r="C145" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Mustafa</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Doğan</v>
+      </c>
+      <c r="C146" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>Tanaz</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Hafezi</v>
+      </c>
+      <c r="C147" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Bünyamin</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Doğan</v>
+      </c>
+      <c r="C148" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Mergim</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Jusufi</v>
+      </c>
+      <c r="C149" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Ahrens</v>
+      </c>
+      <c r="C150" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Flora</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Ahrens</v>
+      </c>
+      <c r="C151" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Artur</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Tovmasian</v>
+      </c>
+      <c r="C152" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Julian</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Krutki</v>
+      </c>
+      <c r="C153" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>Zoe</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Buder</v>
+      </c>
+      <c r="C154" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Antony</v>
+      </c>
+      <c r="B155" t="str">
+        <v/>
+      </c>
+      <c r="C155" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Laura</v>
+      </c>
+      <c r="B156" t="str">
+        <v/>
+      </c>
+      <c r="C156" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Ali</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Haj Ali</v>
+      </c>
+      <c r="C157" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Kenan</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Erdem</v>
+      </c>
+      <c r="C158" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Hazar</v>
+      </c>
+      <c r="B159" t="str">
+        <v/>
+      </c>
+      <c r="C159" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Açelya</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Yildiz</v>
+      </c>
+      <c r="C160" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>Muhammed</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Yildiz</v>
+      </c>
+      <c r="C161" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Kutay</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Pamuk</v>
+      </c>
+      <c r="C162" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Almina</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Varsak</v>
+      </c>
+      <c r="C163" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Görkem</v>
+      </c>
+      <c r="B164" t="str">
+        <v/>
+      </c>
+      <c r="C164" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Elif</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Türk</v>
+      </c>
+      <c r="C165" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Metin</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Kilinc</v>
+      </c>
+      <c r="C166" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Erdogan</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Yilmaz</v>
+      </c>
+      <c r="C167" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Umur</v>
+      </c>
+      <c r="B168" t="str">
+        <v/>
+      </c>
+      <c r="C168" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>Phillip</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Schulz</v>
+      </c>
+      <c r="C169" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Lilia</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Schulz</v>
+      </c>
+      <c r="C170" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Philipp</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Scheffler</v>
+      </c>
+      <c r="C171" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Vahan</v>
+      </c>
+      <c r="B172" t="str">
+        <v/>
+      </c>
+      <c r="C172" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>Eser</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Avci</v>
+      </c>
+      <c r="C173" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>Lena</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Brüggmann</v>
+      </c>
+      <c r="C174" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>Fatih</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Kara</v>
+      </c>
+      <c r="C175" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>Jacqueline</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Kara</v>
+      </c>
+      <c r="C176" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Ravael</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Koch</v>
+      </c>
+      <c r="C177" t="str">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C177"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -1559,7 +1559,7 @@
         <v>Hamit</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Cesur</v>
       </c>
       <c r="C106" t="str">
         <v>14</v>

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -418,7 +418,7 @@
         <v>Demirci</v>
       </c>
       <c r="C2" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +429,7 @@
         <v>Demirci</v>
       </c>
       <c r="C3" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="4">
@@ -440,7 +440,7 @@
         <v>Schner</v>
       </c>
       <c r="C4" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>Schner</v>
       </c>
       <c r="C5" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="6">
@@ -462,7 +462,7 @@
         <v>Brandt</v>
       </c>
       <c r="C6" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>Toplar</v>
       </c>
       <c r="C7" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="8">
@@ -484,7 +484,7 @@
         <v>Toplar</v>
       </c>
       <c r="C8" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="9">
@@ -495,7 +495,7 @@
         <v>Demirci</v>
       </c>
       <c r="C9" t="str">
-        <v>1</v>
+        <v>Tisch 1</v>
       </c>
     </row>
     <row r="10">

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:C176"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -506,7 +506,7 @@
         <v>Bente</v>
       </c>
       <c r="C10" t="str">
-        <v>2</v>
+        <v>Tisch 2</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>Bente</v>
       </c>
       <c r="C11" t="str">
-        <v>2</v>
+        <v>Tisch 2</v>
       </c>
     </row>
     <row r="12">
@@ -528,7 +528,7 @@
         <v>Bente</v>
       </c>
       <c r="C12" t="str">
-        <v>2</v>
+        <v>Tisch 2</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>Gurok</v>
       </c>
       <c r="C13" t="str">
-        <v>2</v>
+        <v>Tisch 2</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         <v>Möller</v>
       </c>
       <c r="C14" t="str">
-        <v>2</v>
+        <v>Tisch 2</v>
       </c>
     </row>
     <row r="15">
@@ -561,7 +561,7 @@
         <v>Möller</v>
       </c>
       <c r="C15" t="str">
-        <v>2</v>
+        <v>Tisch 2</v>
       </c>
     </row>
     <row r="16">
@@ -572,7 +572,7 @@
         <v>Möller</v>
       </c>
       <c r="C16" t="str">
-        <v>2</v>
+        <v>Tisch 2</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         <v>Hansen</v>
       </c>
       <c r="C17" t="str">
-        <v>3</v>
+        <v>Tisch 3</v>
       </c>
     </row>
     <row r="18">
@@ -594,7 +594,7 @@
         <v>Eckert</v>
       </c>
       <c r="C18" t="str">
-        <v>3</v>
+        <v>Tisch 3</v>
       </c>
     </row>
     <row r="19">
@@ -605,7 +605,7 @@
         <v>Eckert</v>
       </c>
       <c r="C19" t="str">
-        <v>3</v>
+        <v>Tisch 3</v>
       </c>
     </row>
     <row r="20">
@@ -616,7 +616,7 @@
         <v>Schröder</v>
       </c>
       <c r="C20" t="str">
-        <v>3</v>
+        <v>Tisch 3</v>
       </c>
     </row>
     <row r="21">
@@ -627,1728 +627,1717 @@
         <v>Hansen</v>
       </c>
       <c r="C21" t="str">
-        <v>3</v>
+        <v>Tisch 3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Olaf</v>
+        <v>Tim</v>
       </c>
       <c r="B22" t="str">
-        <v>Freundin</v>
+        <v>Salenz</v>
       </c>
       <c r="C22" t="str">
-        <v>3</v>
+        <v>Tisch 3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tim</v>
+        <v>Hannah</v>
       </c>
       <c r="B23" t="str">
         <v>Salenz</v>
       </c>
       <c r="C23" t="str">
-        <v>3</v>
+        <v>Tisch 3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Hannah</v>
+        <v>Matthias</v>
       </c>
       <c r="B24" t="str">
-        <v>Salenz</v>
+        <v>Bente</v>
       </c>
       <c r="C24" t="str">
-        <v>3</v>
+        <v>Tisch 4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Matthias</v>
+        <v>Bettina</v>
       </c>
       <c r="B25" t="str">
         <v>Bente</v>
       </c>
       <c r="C25" t="str">
-        <v>4</v>
+        <v>Tisch 4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bettina</v>
+        <v>Katharina</v>
       </c>
       <c r="B26" t="str">
         <v>Bente</v>
       </c>
       <c r="C26" t="str">
-        <v>4</v>
+        <v>Tisch 4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Katharina</v>
+        <v>Antonia</v>
       </c>
       <c r="B27" t="str">
         <v>Bente</v>
       </c>
       <c r="C27" t="str">
-        <v>4</v>
+        <v>Tisch 4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Antonia</v>
+        <v>Gaby</v>
       </c>
       <c r="B28" t="str">
         <v>Bente</v>
       </c>
       <c r="C28" t="str">
-        <v>4</v>
+        <v>Tisch 4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Gaby</v>
+        <v>Rüdiger</v>
       </c>
       <c r="B29" t="str">
         <v>Bente</v>
       </c>
       <c r="C29" t="str">
-        <v>4</v>
+        <v>Tisch 4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Rüdiger</v>
+        <v>Annem</v>
       </c>
       <c r="B30" t="str">
-        <v>Bente</v>
+        <v>Demirci</v>
       </c>
       <c r="C30" t="str">
-        <v>4</v>
+        <v>Tisch 5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Annem</v>
+        <v>Babam</v>
       </c>
       <c r="B31" t="str">
         <v>Demirci</v>
       </c>
       <c r="C31" t="str">
-        <v>5</v>
+        <v>Tisch 5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Babam</v>
+        <v>Serpil</v>
       </c>
       <c r="B32" t="str">
-        <v>Demirci</v>
+        <v>Dogukan</v>
       </c>
       <c r="C32" t="str">
-        <v>5</v>
+        <v>Tisch 5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Serpil</v>
+        <v>Süleymann</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Dogukan</v>
       </c>
       <c r="C33" t="str">
-        <v>5</v>
+        <v>Tisch 5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Süleymann</v>
+        <v>Berksan</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Yurtsever</v>
       </c>
       <c r="C34" t="str">
-        <v>5</v>
+        <v>Tisch 5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Berksan</v>
+        <v>Emin</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Yurtsever</v>
       </c>
       <c r="C35" t="str">
-        <v>5</v>
+        <v>Tisch 5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Emin</v>
+        <v>Aslihan</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Dogukan</v>
       </c>
       <c r="C36" t="str">
-        <v>5</v>
+        <v>Tisch 5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Aslihan</v>
+        <v>Mehmet</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Demirci</v>
       </c>
       <c r="C37" t="str">
-        <v>5</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Mehmet</v>
+        <v>Zeynep</v>
       </c>
       <c r="B38" t="str">
         <v>Demirci</v>
       </c>
       <c r="C38" t="str">
-        <v>6</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Zeynep</v>
+        <v>Emircan</v>
       </c>
       <c r="B39" t="str">
         <v>Demirci</v>
       </c>
       <c r="C39" t="str">
-        <v>6</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Emerican</v>
+        <v>Sahin</v>
       </c>
       <c r="B40" t="str">
         <v>Demirci</v>
       </c>
       <c r="C40" t="str">
-        <v>6</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Sahin</v>
+        <v>Sidica</v>
       </c>
       <c r="B41" t="str">
         <v>Demirci</v>
       </c>
       <c r="C41" t="str">
-        <v>6</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Sidica</v>
+        <v>Yasin</v>
       </c>
       <c r="B42" t="str">
-        <v>Demirci</v>
+        <v>Demrici</v>
       </c>
       <c r="C42" t="str">
-        <v>6</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Yasin</v>
+        <v>Yasim</v>
       </c>
       <c r="B43" t="str">
         <v>Demrici</v>
       </c>
       <c r="C43" t="str">
-        <v>6</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Yasim</v>
+        <v>Eda</v>
       </c>
       <c r="B44" t="str">
-        <v>Demrici</v>
+        <v>Demirci</v>
       </c>
       <c r="C44" t="str">
-        <v>6</v>
+        <v>Tisch 6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Eda</v>
+        <v>Jenny</v>
       </c>
       <c r="B45" t="str">
-        <v>Demirci</v>
+        <v>Brandt</v>
       </c>
       <c r="C45" t="str">
-        <v>6</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Jenny</v>
+        <v>Behram</v>
       </c>
       <c r="B46" t="str">
-        <v>Brandt</v>
+        <v>Karakan</v>
       </c>
       <c r="C46" t="str">
-        <v>7</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Behram</v>
+        <v>Naima</v>
       </c>
       <c r="B47" t="str">
         <v>Brandt</v>
       </c>
       <c r="C47" t="str">
-        <v>7</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Naima</v>
+        <v>Nico</v>
       </c>
       <c r="B48" t="str">
-        <v>Brandt</v>
+        <v>Bethien</v>
       </c>
       <c r="C48" t="str">
-        <v>7</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nico</v>
+        <v>Yasin</v>
       </c>
       <c r="B49" t="str">
-        <v>Bethien</v>
+        <v>Brandt</v>
       </c>
       <c r="C49" t="str">
-        <v>7</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Yasin</v>
+        <v>Lara</v>
       </c>
       <c r="B50" t="str">
-        <v>Brandt</v>
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v>7</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lara</v>
+        <v>Nicole</v>
       </c>
       <c r="B51" t="str">
-        <v/>
+        <v>Vukmirovic</v>
       </c>
       <c r="C51" t="str">
-        <v>7</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nicole</v>
+        <v>Adrian</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Vukmirovic</v>
       </c>
       <c r="C52" t="str">
-        <v>7</v>
+        <v>Tisch 7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Adrian</v>
+        <v>Laura</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Peters</v>
       </c>
       <c r="C53" t="str">
-        <v>7</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Laura</v>
+        <v>Michael</v>
       </c>
       <c r="B54" t="str">
-        <v>Peters</v>
+        <v>Weber</v>
       </c>
       <c r="C54" t="str">
-        <v>8</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Michael</v>
+        <v>Saskia</v>
       </c>
       <c r="B55" t="str">
-        <v>Weber</v>
+        <v>Knop</v>
       </c>
       <c r="C55" t="str">
-        <v>8</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Saskia</v>
+        <v>Fabian</v>
       </c>
       <c r="B56" t="str">
-        <v>Knop</v>
+        <v>Bethien</v>
       </c>
       <c r="C56" t="str">
-        <v>8</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Fabian</v>
+        <v>Liliane</v>
       </c>
       <c r="B57" t="str">
-        <v>Bethien</v>
+        <v>Ullrich</v>
       </c>
       <c r="C57" t="str">
-        <v>8</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lili</v>
+        <v>Henriette</v>
       </c>
       <c r="B58" t="str">
-        <v>Ulrich</v>
+        <v>Niermann</v>
       </c>
       <c r="C58" t="str">
-        <v>8</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Henriette</v>
+        <v>Antonia</v>
       </c>
       <c r="B59" t="str">
-        <v>Niermann</v>
+        <v>Schultz</v>
       </c>
       <c r="C59" t="str">
-        <v>8</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Antonia</v>
+        <v>Kevin</v>
       </c>
       <c r="B60" t="str">
-        <v>Schultz</v>
+        <v>Klemm</v>
       </c>
       <c r="C60" t="str">
-        <v>8</v>
+        <v>Tisch 8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Kevin</v>
+        <v>Caroline</v>
       </c>
       <c r="B61" t="str">
-        <v>Klemm</v>
+        <v>Schnelle</v>
       </c>
       <c r="C61" t="str">
-        <v>8</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Caroline</v>
+        <v>Moritz</v>
       </c>
       <c r="B62" t="str">
-        <v>Schnelle</v>
+        <v>Großmann</v>
       </c>
       <c r="C62" t="str">
-        <v>9</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Moritz</v>
+        <v>Marvin</v>
       </c>
       <c r="B63" t="str">
-        <v>Großmann</v>
+        <v>Loeding</v>
       </c>
       <c r="C63" t="str">
-        <v>9</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Marvin</v>
+        <v>Christina</v>
       </c>
       <c r="B64" t="str">
-        <v>Loeding</v>
+        <v>Stamp</v>
       </c>
       <c r="C64" t="str">
-        <v>9</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Christina</v>
+        <v>Anton</v>
       </c>
       <c r="B65" t="str">
-        <v>Stamp</v>
+        <v>Offner</v>
       </c>
       <c r="C65" t="str">
-        <v>9</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Anton</v>
+        <v>Mila</v>
       </c>
       <c r="B66" t="str">
-        <v>Offner</v>
+        <v>Gastmann</v>
       </c>
       <c r="C66" t="str">
-        <v>9</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mila</v>
+        <v>Merle</v>
       </c>
       <c r="B67" t="str">
-        <v>Gastmann</v>
+        <v>Lehmann</v>
       </c>
       <c r="C67" t="str">
-        <v>9</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Merle</v>
+        <v>Aileen</v>
       </c>
       <c r="B68" t="str">
-        <v>Lehmann</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>9</v>
+        <v>Tisch 9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Aileen</v>
+        <v>Muzaffer</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Toplar</v>
       </c>
       <c r="C69" t="str">
-        <v>9</v>
+        <v>Tisch 10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Hacer</v>
       </c>
       <c r="B70" t="str">
         <v>Toplar</v>
       </c>
       <c r="C70" t="str">
-        <v>10</v>
+        <v>Tisch 10</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v/>
+        <v>Bahar</v>
       </c>
       <c r="B71" t="str">
         <v>Toplar</v>
       </c>
       <c r="C71" t="str">
-        <v>10</v>
+        <v>Tisch 10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bahar</v>
+        <v>Merve</v>
       </c>
       <c r="B72" t="str">
         <v>Toplar</v>
       </c>
       <c r="C72" t="str">
-        <v>10</v>
+        <v>Tisch 10</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Merve</v>
+        <v>Mohammed</v>
       </c>
       <c r="B73" t="str">
         <v>Toplar</v>
       </c>
       <c r="C73" t="str">
-        <v>10</v>
+        <v>Tisch 10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Muhammed</v>
+        <v>Hanifi</v>
       </c>
       <c r="B74" t="str">
         <v>Toplar</v>
       </c>
       <c r="C74" t="str">
-        <v>10</v>
+        <v>Tisch 10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Hanifi</v>
+        <v>Nadine</v>
       </c>
       <c r="B75" t="str">
         <v>Toplar</v>
       </c>
       <c r="C75" t="str">
-        <v>10</v>
+        <v>Tisch 10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Nadine</v>
+        <v>Ali</v>
       </c>
       <c r="B76" t="str">
-        <v>Toplar</v>
+        <v>Sancak</v>
       </c>
       <c r="C76" t="str">
-        <v>10</v>
+        <v>Tisch 11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ali</v>
+        <v>Navjot</v>
       </c>
       <c r="B77" t="str">
         <v>Sancak</v>
       </c>
       <c r="C77" t="str">
-        <v>11</v>
+        <v>Tisch 11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Navjot</v>
+        <v>Semih</v>
       </c>
       <c r="B78" t="str">
-        <v>Sancak</v>
+        <v>Çakmakcı</v>
       </c>
       <c r="C78" t="str">
-        <v>11</v>
+        <v>Tisch 11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Semih</v>
+        <v>Asli</v>
       </c>
       <c r="B79" t="str">
         <v>Çakmakcı</v>
       </c>
       <c r="C79" t="str">
-        <v>11</v>
+        <v>Tisch 11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Asli</v>
+        <v>Yunus</v>
       </c>
       <c r="B80" t="str">
-        <v>Çakmakcı</v>
+        <v>Motorrad</v>
       </c>
       <c r="C80" t="str">
-        <v>11</v>
+        <v>Tisch 11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Yunus</v>
+        <v>Fatih</v>
       </c>
       <c r="B81" t="str">
         <v>Motorrad</v>
       </c>
       <c r="C81" t="str">
-        <v>11</v>
+        <v>Tisch 11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Fatih</v>
+        <v>Aliye</v>
       </c>
       <c r="B82" t="str">
-        <v>Motorrad</v>
+        <v>Avci</v>
       </c>
       <c r="C82" t="str">
-        <v>11</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Aliye</v>
+        <v>Nazli</v>
       </c>
       <c r="B83" t="str">
         <v>Avci</v>
       </c>
       <c r="C83" t="str">
-        <v>12</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Nazli</v>
+        <v>Mehmet</v>
       </c>
       <c r="B84" t="str">
         <v>Avci</v>
       </c>
       <c r="C84" t="str">
-        <v>12</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mehmet</v>
+        <v>Ayten</v>
       </c>
       <c r="B85" t="str">
-        <v>Avci</v>
+        <v>Müller</v>
       </c>
       <c r="C85" t="str">
-        <v>12</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Ayten</v>
+        <v>Mira</v>
       </c>
       <c r="B86" t="str">
         <v>Müller</v>
       </c>
       <c r="C86" t="str">
-        <v>12</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Mira</v>
+        <v>Leyla</v>
       </c>
       <c r="B87" t="str">
         <v>Müller</v>
       </c>
       <c r="C87" t="str">
-        <v>12</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Leyla</v>
+        <v>Deniz</v>
       </c>
       <c r="B88" t="str">
-        <v>Müller</v>
+        <v>Üyen</v>
       </c>
       <c r="C88" t="str">
-        <v>12</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Deniz</v>
+        <v>Nazli</v>
       </c>
       <c r="B89" t="str">
         <v>Üyen</v>
       </c>
       <c r="C89" t="str">
-        <v>12</v>
+        <v>Tisch 12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nazli</v>
+        <v>Melek</v>
       </c>
       <c r="B90" t="str">
-        <v>Üyen</v>
+        <v>Yilmaz</v>
       </c>
       <c r="C90" t="str">
-        <v>12</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Melek</v>
+        <v>Ali</v>
       </c>
       <c r="B91" t="str">
         <v>Yilmaz</v>
       </c>
       <c r="C91" t="str">
-        <v>13</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Ali</v>
+        <v>Hilal</v>
       </c>
       <c r="B92" t="str">
-        <v>Yilmaz</v>
+        <v>Bektas</v>
       </c>
       <c r="C92" t="str">
-        <v>13</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Hilal</v>
+        <v>Eren</v>
       </c>
       <c r="B93" t="str">
         <v>Bektas</v>
       </c>
       <c r="C93" t="str">
-        <v>13</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Eren</v>
+        <v>Sultan</v>
       </c>
       <c r="B94" t="str">
-        <v>Bektas</v>
+        <v>Aksoy</v>
       </c>
       <c r="C94" t="str">
-        <v>13</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sultan</v>
+        <v>Seyma</v>
       </c>
       <c r="B95" t="str">
         <v>Aksoy</v>
       </c>
       <c r="C95" t="str">
-        <v>13</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Seyma</v>
+        <v>Cevriye</v>
       </c>
       <c r="B96" t="str">
-        <v>Aksoy</v>
+        <v>Seyhan</v>
       </c>
       <c r="C96" t="str">
-        <v>13</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Cevriye</v>
+        <v>Durgadin</v>
       </c>
       <c r="B97" t="str">
-        <v>Seyhan</v>
+        <v>Bolat</v>
       </c>
       <c r="C97" t="str">
-        <v>13</v>
+        <v>Tisch 13</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Durgadin</v>
+        <v>Mahmut</v>
       </c>
       <c r="B98" t="str">
-        <v>Bolat</v>
+        <v>Yildiz</v>
       </c>
       <c r="C98" t="str">
-        <v>13</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Mahmut</v>
+        <v>Mehmet</v>
       </c>
       <c r="B99" t="str">
         <v>Yildiz</v>
       </c>
       <c r="C99" t="str">
-        <v>14</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Mehmet</v>
+        <v>Serdal</v>
       </c>
       <c r="B100" t="str">
-        <v>Yildiz</v>
+        <v>Sahin</v>
       </c>
       <c r="C100" t="str">
-        <v>14</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Serdal</v>
+        <v>Saziye</v>
       </c>
       <c r="B101" t="str">
         <v>Sahin</v>
       </c>
       <c r="C101" t="str">
-        <v>14</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Saziye</v>
+        <v>Sinan</v>
       </c>
       <c r="B102" t="str">
-        <v>Sahin</v>
+        <v>Oruclu</v>
       </c>
       <c r="C102" t="str">
-        <v>14</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Sinan</v>
+        <v>Emsal</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>Oruclu</v>
       </c>
       <c r="C103" t="str">
-        <v>14</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Emsal</v>
+        <v>Vildan</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>Oruclu</v>
       </c>
       <c r="C104" t="str">
-        <v>14</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Vildan</v>
+        <v>Hamit</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Cesur</v>
       </c>
       <c r="C105" t="str">
-        <v>14</v>
+        <v>Tisch 14</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Hamit</v>
+        <v>Miriyam</v>
       </c>
       <c r="B106" t="str">
-        <v>Cesur</v>
+        <v>Rahimi</v>
       </c>
       <c r="C106" t="str">
-        <v>14</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Miriyam</v>
+        <v>Ali</v>
       </c>
       <c r="B107" t="str">
         <v>Rahimi</v>
       </c>
       <c r="C107" t="str">
-        <v>15</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Ali</v>
+        <v>Kacper</v>
       </c>
       <c r="B108" t="str">
-        <v>Rahimi</v>
+        <v>Nowak</v>
       </c>
       <c r="C108" t="str">
-        <v>15</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Kacper</v>
+        <v>Leonie</v>
       </c>
       <c r="B109" t="str">
-        <v>Nowak</v>
+        <v>Paulsen</v>
       </c>
       <c r="C109" t="str">
-        <v>15</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Leonie</v>
+        <v>Özlem</v>
       </c>
       <c r="B110" t="str">
-        <v>Paulsen</v>
+        <v>Yuvali</v>
       </c>
       <c r="C110" t="str">
-        <v>15</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Özlem</v>
+        <v>Kubilay-Alpay</v>
       </c>
       <c r="B111" t="str">
         <v>Yuvali</v>
       </c>
       <c r="C111" t="str">
-        <v>15</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Kubilay-Alpay</v>
+        <v>Ibrahim</v>
       </c>
       <c r="B112" t="str">
-        <v>Yuvali</v>
+        <v>Özcan</v>
       </c>
       <c r="C112" t="str">
-        <v>15</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Ibrahim</v>
+        <v>Rezal</v>
       </c>
       <c r="B113" t="str">
-        <v>Özcan</v>
+        <v>Yosofi</v>
       </c>
       <c r="C113" t="str">
-        <v>15</v>
+        <v>Tisch 15</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Rezal</v>
+        <v>Hanno</v>
       </c>
       <c r="B114" t="str">
-        <v>Yosofi</v>
+        <v>Rencken</v>
       </c>
       <c r="C114" t="str">
-        <v>15</v>
+        <v>Tisch 16</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Hanno</v>
+        <v>Svende</v>
       </c>
       <c r="B115" t="str">
-        <v>Rencken</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>16</v>
+        <v>Tisch 16</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Svende</v>
+        <v>Robert</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>Ladewig</v>
       </c>
       <c r="C116" t="str">
-        <v>16</v>
+        <v>Tisch 16</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Robert</v>
+        <v>Lukas</v>
       </c>
       <c r="B117" t="str">
-        <v>Ladewig</v>
+        <v>Tiede</v>
       </c>
       <c r="C117" t="str">
-        <v>16</v>
+        <v>Tisch 16</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Lukas</v>
+        <v>Patrik</v>
       </c>
       <c r="B118" t="str">
-        <v>Tiede</v>
+        <v>Kunkel</v>
       </c>
       <c r="C118" t="str">
-        <v>16</v>
+        <v>Tisch 16</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Paddy</v>
+        <v>Daniel</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>Lizenberger</v>
       </c>
       <c r="C119" t="str">
-        <v>16</v>
+        <v>Tisch 16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Daniel</v>
+        <v>Michi</v>
       </c>
       <c r="B120" t="str">
-        <v>Litzenberger</v>
+        <v>Nissen</v>
       </c>
       <c r="C120" t="str">
-        <v>16</v>
+        <v>Tisch 17</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Michi</v>
+        <v>Nici</v>
       </c>
       <c r="B121" t="str">
         <v>Nissen</v>
       </c>
       <c r="C121" t="str">
-        <v>17</v>
+        <v>Tisch 17</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Nici</v>
+        <v>Sebastian</v>
       </c>
       <c r="B122" t="str">
-        <v>Nissen</v>
+        <v>Hansen</v>
       </c>
       <c r="C122" t="str">
-        <v>17</v>
+        <v>Tisch 17</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sebastian</v>
+        <v>Imke</v>
       </c>
       <c r="B123" t="str">
         <v>Hansen</v>
       </c>
       <c r="C123" t="str">
-        <v>17</v>
+        <v>Tisch 17</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Imke</v>
+        <v>Rıdvan</v>
       </c>
       <c r="B124" t="str">
-        <v>Hansen</v>
+        <v>Canbul</v>
       </c>
       <c r="C124" t="str">
-        <v>17</v>
+        <v>Tisch 17</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Ridvan</v>
+        <v>Nurgül</v>
       </c>
       <c r="B125" t="str">
         <v>Canbul</v>
       </c>
       <c r="C125" t="str">
-        <v>17</v>
+        <v>Tisch 17</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Nurgül</v>
+        <v>Fatih</v>
       </c>
       <c r="B126" t="str">
-        <v>Canbul</v>
+        <v>Balkas</v>
       </c>
       <c r="C126" t="str">
-        <v>17</v>
+        <v>Tisch 17</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Fatih</v>
+        <v>Mirko</v>
       </c>
       <c r="B127" t="str">
-        <v>Balkas</v>
+        <v>Niemann</v>
       </c>
       <c r="C127" t="str">
-        <v>17</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Mirko</v>
+        <v>Anissa</v>
       </c>
       <c r="B128" t="str">
         <v>Niemann</v>
       </c>
       <c r="C128" t="str">
-        <v>18</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Anissa</v>
+        <v>Arne</v>
       </c>
       <c r="B129" t="str">
-        <v>Niemann</v>
+        <v>Steinfatt</v>
       </c>
       <c r="C129" t="str">
-        <v>18</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Arne</v>
+        <v>Sarah</v>
       </c>
       <c r="B130" t="str">
         <v>Steinfatt</v>
       </c>
       <c r="C130" t="str">
-        <v>18</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sarah</v>
+        <v>Marcel</v>
       </c>
       <c r="B131" t="str">
-        <v>Steinfatt</v>
+        <v>Petersen</v>
       </c>
       <c r="C131" t="str">
-        <v>18</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Marcel</v>
+        <v>Stefanie</v>
       </c>
       <c r="B132" t="str">
         <v>Petersen</v>
       </c>
       <c r="C132" t="str">
-        <v>18</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Stefanie</v>
+        <v>Serhat</v>
       </c>
       <c r="B133" t="str">
-        <v>Petersen</v>
+        <v>Bakan</v>
       </c>
       <c r="C133" t="str">
-        <v>18</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Serhat</v>
+        <v>Yasemin</v>
       </c>
       <c r="B134" t="str">
         <v>Bakan</v>
       </c>
       <c r="C134" t="str">
-        <v>18</v>
+        <v>Tisch 18</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Yasemin</v>
+        <v>Aras</v>
       </c>
       <c r="B135" t="str">
-        <v>Bakan</v>
+        <v/>
       </c>
       <c r="C135" t="str">
-        <v>18</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Aras</v>
+        <v>Kausar</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>19</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Kausar</v>
+        <v>Lawand</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>19</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Lawand</v>
+        <v>Fetanet</v>
       </c>
       <c r="B138" t="str">
-        <v/>
+        <v>Aksoy</v>
       </c>
       <c r="C138" t="str">
-        <v>19</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Fetanet</v>
+        <v>Adem</v>
       </c>
       <c r="B139" t="str">
-        <v>Aksoy</v>
+        <v>Erim</v>
       </c>
       <c r="C139" t="str">
-        <v>19</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Adem</v>
+        <v>Isa</v>
       </c>
       <c r="B140" t="str">
         <v>Erim</v>
       </c>
       <c r="C140" t="str">
-        <v>19</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Isa</v>
+        <v>Wasim</v>
       </c>
       <c r="B141" t="str">
-        <v>Erim</v>
+        <v>Haj Ali</v>
       </c>
       <c r="C141" t="str">
-        <v>19</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Wasim</v>
+        <v>Jessica</v>
       </c>
       <c r="B142" t="str">
         <v>Haj Ali</v>
       </c>
       <c r="C142" t="str">
-        <v>19</v>
+        <v>Tisch 19</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Jessica</v>
+        <v>Emrah</v>
       </c>
       <c r="B143" t="str">
-        <v>Haj Ali</v>
+        <v>Üyen</v>
       </c>
       <c r="C143" t="str">
-        <v>19</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Emrah</v>
+        <v>Baran</v>
       </c>
       <c r="B144" t="str">
-        <v/>
+        <v>Bingöl</v>
       </c>
       <c r="C144" t="str">
-        <v>20</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Baran</v>
+        <v>Mustafa</v>
       </c>
       <c r="B145" t="str">
-        <v/>
+        <v>Doğan</v>
       </c>
       <c r="C145" t="str">
-        <v>20</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Mustafa</v>
+        <v>Tanaz</v>
       </c>
       <c r="B146" t="str">
-        <v>Doğan</v>
+        <v>Hafezi</v>
       </c>
       <c r="C146" t="str">
-        <v>20</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Tanaz</v>
+        <v>Bünyamin</v>
       </c>
       <c r="B147" t="str">
-        <v>Hafezi</v>
+        <v>Doğan</v>
       </c>
       <c r="C147" t="str">
-        <v>20</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Bünyamin</v>
+        <v>Mergim</v>
       </c>
       <c r="B148" t="str">
-        <v>Doğan</v>
+        <v>Jusufi</v>
       </c>
       <c r="C148" t="str">
-        <v>20</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Mergim</v>
+        <v>Alexander</v>
       </c>
       <c r="B149" t="str">
-        <v>Jusufi</v>
+        <v>Ahrens</v>
       </c>
       <c r="C149" t="str">
-        <v>20</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Alexander</v>
+        <v>Flora</v>
       </c>
       <c r="B150" t="str">
         <v>Ahrens</v>
       </c>
       <c r="C150" t="str">
-        <v>20</v>
+        <v>Tisch 20</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Flora</v>
+        <v>Artur</v>
       </c>
       <c r="B151" t="str">
-        <v>Ahrens</v>
+        <v>Tovmasian</v>
       </c>
       <c r="C151" t="str">
-        <v>20</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Artur</v>
+        <v>Julian</v>
       </c>
       <c r="B152" t="str">
-        <v>Tovmasian</v>
+        <v>Krutki</v>
       </c>
       <c r="C152" t="str">
-        <v>21</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Julian</v>
+        <v>Zoe</v>
       </c>
       <c r="B153" t="str">
-        <v>Krutki</v>
+        <v>Buder</v>
       </c>
       <c r="C153" t="str">
-        <v>21</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Zoe</v>
+        <v>Antony</v>
       </c>
       <c r="B154" t="str">
-        <v>Buder</v>
+        <v/>
       </c>
       <c r="C154" t="str">
-        <v>21</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Antony</v>
+        <v>Laura</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>21</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Laura</v>
+        <v>Ali</v>
       </c>
       <c r="B156" t="str">
-        <v/>
+        <v>Haj Ali</v>
       </c>
       <c r="C156" t="str">
-        <v>21</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ali</v>
+        <v>Kenan</v>
       </c>
       <c r="B157" t="str">
-        <v>Haj Ali</v>
+        <v>Erdem</v>
       </c>
       <c r="C157" t="str">
-        <v>21</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Kenan</v>
+        <v>Hazar</v>
       </c>
       <c r="B158" t="str">
-        <v>Erdem</v>
+        <v>Güney</v>
       </c>
       <c r="C158" t="str">
-        <v>21</v>
+        <v>Tisch 21</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Hazar</v>
+        <v>Açelya</v>
       </c>
       <c r="B159" t="str">
-        <v/>
+        <v>Yildiz</v>
       </c>
       <c r="C159" t="str">
-        <v>21</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Açelya</v>
+        <v>Muhammed</v>
       </c>
       <c r="B160" t="str">
         <v>Yildiz</v>
       </c>
       <c r="C160" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Muhammed</v>
+        <v>Kutay</v>
       </c>
       <c r="B161" t="str">
-        <v>Yildiz</v>
+        <v>Pamuk</v>
       </c>
       <c r="C161" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Kutay</v>
+        <v>Almina</v>
       </c>
       <c r="B162" t="str">
-        <v>Pamuk</v>
+        <v>Varsak</v>
       </c>
       <c r="C162" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Almina</v>
+        <v>Görkem</v>
       </c>
       <c r="B163" t="str">
-        <v>Varsak</v>
+        <v>Sen</v>
       </c>
       <c r="C163" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Görkem</v>
+        <v>Ebru Elif</v>
       </c>
       <c r="B164" t="str">
-        <v/>
+        <v>Türk</v>
       </c>
       <c r="C164" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Elif</v>
+        <v>Metin</v>
       </c>
       <c r="B165" t="str">
-        <v>Türk</v>
+        <v>Kilinc</v>
       </c>
       <c r="C165" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Metin</v>
+        <v>Erdogan</v>
       </c>
       <c r="B166" t="str">
-        <v>Kilinc</v>
+        <v>Yilmaz</v>
       </c>
       <c r="C166" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Erdogan</v>
+        <v>Umur</v>
       </c>
       <c r="B167" t="str">
-        <v>Yilmaz</v>
+        <v>Dogan</v>
       </c>
       <c r="C167" t="str">
-        <v>22</v>
+        <v>Tisch 22</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Umur</v>
+        <v>Phillip</v>
       </c>
       <c r="B168" t="str">
-        <v/>
+        <v>Schulz</v>
       </c>
       <c r="C168" t="str">
-        <v>22</v>
+        <v>Tisch 23</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Phillip</v>
+        <v>Lilia</v>
       </c>
       <c r="B169" t="str">
         <v>Schulz</v>
       </c>
       <c r="C169" t="str">
-        <v>23</v>
+        <v>Tisch 23</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Lilia</v>
+        <v>Philipp</v>
       </c>
       <c r="B170" t="str">
-        <v>Schulz</v>
+        <v>Scheffler</v>
       </c>
       <c r="C170" t="str">
-        <v>23</v>
+        <v>Tisch 23</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Philipp</v>
+        <v>Vahan</v>
       </c>
       <c r="B171" t="str">
-        <v>Scheffler</v>
+        <v>Doriyan</v>
       </c>
       <c r="C171" t="str">
-        <v>23</v>
+        <v>Tisch 23</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Vahan</v>
+        <v>Eser</v>
       </c>
       <c r="B172" t="str">
-        <v/>
+        <v>Avci</v>
       </c>
       <c r="C172" t="str">
-        <v>23</v>
+        <v>Tisch 24</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Eser</v>
+        <v>Lena</v>
       </c>
       <c r="B173" t="str">
-        <v>Avci</v>
+        <v>Brüggmann</v>
       </c>
       <c r="C173" t="str">
-        <v>24</v>
+        <v>Tisch 24</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Lena</v>
+        <v>Fatih</v>
       </c>
       <c r="B174" t="str">
-        <v>Brüggmann</v>
+        <v>Kara</v>
       </c>
       <c r="C174" t="str">
-        <v>24</v>
+        <v>Tisch 24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Fatih</v>
+        <v>Jacqueline</v>
       </c>
       <c r="B175" t="str">
         <v>Kara</v>
       </c>
       <c r="C175" t="str">
-        <v>24</v>
+        <v>Tisch 24</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Jacqueline</v>
+        <v>Ravael</v>
       </c>
       <c r="B176" t="str">
-        <v>Kara</v>
+        <v>Koch</v>
       </c>
       <c r="C176" t="str">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>Ravael</v>
-      </c>
-      <c r="B177" t="str">
-        <v>Koch</v>
-      </c>
-      <c r="C177" t="str">
-        <v>24</v>
+        <v>Tisch 24</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C177"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C176"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C176"/>
+  <dimension ref="A1:C181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -753,7 +753,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Süleymann</v>
+        <v>Süleyman</v>
       </c>
       <c r="B33" t="str">
         <v>Dogukan</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Mohammed</v>
+        <v>Muhammed</v>
       </c>
       <c r="B73" t="str">
         <v>Toplar</v>
@@ -2288,7 +2288,7 @@
         <v>Avci</v>
       </c>
       <c r="C172" t="str">
-        <v>Tisch 24</v>
+        <v>Tisch 23</v>
       </c>
     </row>
     <row r="173">
@@ -2299,26 +2299,26 @@
         <v>Brüggmann</v>
       </c>
       <c r="C173" t="str">
-        <v>Tisch 24</v>
+        <v>Tisch 23</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Fatih</v>
+        <v>Ravael</v>
       </c>
       <c r="B174" t="str">
-        <v>Kara</v>
+        <v>Koch</v>
       </c>
       <c r="C174" t="str">
-        <v>Tisch 24</v>
+        <v>Tisch 23</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Jacqueline</v>
+        <v>Valon</v>
       </c>
       <c r="B175" t="str">
-        <v>Kara</v>
+        <v>Zeqiri</v>
       </c>
       <c r="C175" t="str">
         <v>Tisch 24</v>
@@ -2326,18 +2326,73 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Ravael</v>
+        <v>Valmir</v>
       </c>
       <c r="B176" t="str">
-        <v>Koch</v>
+        <v>Zeqiri</v>
       </c>
       <c r="C176" t="str">
         <v>Tisch 24</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Artur</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Doriyan</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Tisch 24</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Süleyman</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Erim</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Tisch 24</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>Bayram</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Erim</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Tisch 24</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>Muzzafer</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Erim</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Tisch 24</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Can</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Aile</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Tisch 25</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C176"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -2370,7 +2370,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Muzzafer</v>
+        <v>Muzaffer</v>
       </c>
       <c r="B180" t="str">
         <v>Erim</v>

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C180"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2304,18 +2304,18 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Ravael</v>
+        <v>Valon</v>
       </c>
       <c r="B174" t="str">
-        <v>Koch</v>
+        <v>Zeqiri</v>
       </c>
       <c r="C174" t="str">
-        <v>Tisch 23</v>
+        <v>Tisch 24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Valon</v>
+        <v>Valmir</v>
       </c>
       <c r="B175" t="str">
         <v>Zeqiri</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Valmir</v>
+        <v>Artur</v>
       </c>
       <c r="B176" t="str">
-        <v>Zeqiri</v>
+        <v>Doriyan</v>
       </c>
       <c r="C176" t="str">
         <v>Tisch 24</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Artur</v>
+        <v>Süleyman</v>
       </c>
       <c r="B177" t="str">
-        <v>Doriyan</v>
+        <v>Erim</v>
       </c>
       <c r="C177" t="str">
         <v>Tisch 24</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Süleyman</v>
+        <v>Bayram</v>
       </c>
       <c r="B178" t="str">
         <v>Erim</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Bayram</v>
+        <v>Muzaffer</v>
       </c>
       <c r="B179" t="str">
         <v>Erim</v>
@@ -2370,29 +2370,18 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Muzaffer</v>
+        <v>Can</v>
       </c>
       <c r="B180" t="str">
-        <v>Erim</v>
+        <v>Aile</v>
       </c>
       <c r="C180" t="str">
-        <v>Tisch 24</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>Can</v>
-      </c>
-      <c r="B181" t="str">
-        <v>Aile</v>
-      </c>
-      <c r="C181" t="str">
         <v>Tisch 25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C180"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C180"/>
+  <dimension ref="A1:C182"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2373,15 +2373,37 @@
         <v>Can</v>
       </c>
       <c r="B180" t="str">
-        <v>Aile</v>
+        <v>Ailesi</v>
       </c>
       <c r="C180" t="str">
         <v>Tisch 25</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>Güney</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Ailesi</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Tisch 26</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>Şahin</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Ailesi</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Tisch 26</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C180"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C182"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/guests.xlsx
+++ b/guests.xlsx
@@ -1551,7 +1551,7 @@
         <v>Cesur</v>
       </c>
       <c r="C105" t="str">
-        <v>Tisch 14</v>
+        <v>Tisch 24</v>
       </c>
     </row>
     <row r="106">

--- a/guests.xlsx
+++ b/guests.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:C183"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2401,9 +2401,20 @@
         <v>Tisch 26</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>Arva</v>
+      </c>
+      <c r="B183" t="str">
+        <v/>
+      </c>
+      <c r="C183" t="str">
+        <v>Tisch 19</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C182"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C183"/>
   </ignoredErrors>
 </worksheet>
 </file>